--- a/UAT_Excel_Reports/Promo Discount_UAT.xlsx
+++ b/UAT_Excel_Reports/Promo Discount_UAT.xlsx
@@ -66,13 +66,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -439,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,6 +495,1914 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>--- NAVIGATE TO PROMOTIONS LANDING PAGE AND ACCESS PROMOTIONS MANAGEMENT SECTION ---</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>A.1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Navigate to Promotions Landing Page and Access Promotions Management Section</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>A.1.1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Navigate to the Promotions Landing Page</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>`page.goto("https://stage.mkr.esp.antuit.ai/nglcp/promotions/landing-page")`</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>A.1.2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Promotions Action' button</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("promotions-action-button").click()`</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>--- CREATE A NEW PROMOTION AND ENTER BASIC PROMOTION DETAILS (NAME, DESCRIPTION, DATES) ---</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>A.2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Create a New Promotion and Enter Basic Promotion Details</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>A.2.1</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Click on 'New Promotion'</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("New Promotion").click()`</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>A.2.2</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Focus on the 'Promotion Event Name' input field</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("promotionEventName").click()`</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>A.2.3</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Fill in the 'Promotion Event Name' field</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("promotionEventName").fill("rh1230-08-04")`</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>A.2.4</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Focus on the 'Promotion Event Description' input field</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("promotionEventDescription").click()`</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>A.2.5</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Fill in the 'Promotion Event Description' field</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("promotionEventDescription").fill("PROMO DISCOUNT TEST")`</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>A.2.6</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Open the date picker for the 'Start Date' field</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("startDate").click()`</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>A.2.7</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Select the 17th day of the month as the start date</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("17").click()`</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>A.2.8</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Open the date picker for the 'End Date' field</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("endDate").click()`</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>A.2.9</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Select the 18th day of the month as the end date</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("18").click()`</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>--- CONFIGURE PRICING OPTIONS (ASAP PRICING, REGULAR PRICING) ---</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>A.3</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Configure Pricing Options</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>A.3.1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Enable the 'ASAP Pricing' option</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("isAsapPricing").click()`</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>A.3.2</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'Regular Pricing' type</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("price_type_reg").click()`</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>--- APPLY HIERARCHY FILTERS (REGION, PRICE ZONE TYPE, PRICE ZONE) ---</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>A.4</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Apply Hierarchy Filters</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>A.4.1</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Click on the first element in the '.zeb-tiers' section</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".zeb-tiers").first.click()`</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>A.4.2</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'Hierarchy' tab</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Hierarchy$")).nth(3).click()`</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>A.4.3</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Click on the first element in the '.d-flex.p-l-32' section</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".d-flex.p-l-32").first.click()`</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>A.4.4</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'NA' radio button</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("radio", name="NA", exact=True).check()`</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>A.4.5</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Price Zone Type' option</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Price Zone Type").click()`</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>A.4.6</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Select the third checkbox under 'Price Zone Type'</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(3) &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>A.4.7</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Price Zone' option</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Price Zone", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>A.4.8</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Select the first checkbox under 'Price Zone'</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").first.click()`</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>A.4.9</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Revisit the 'Price Zone Type' option</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Price Zone Type").click()`</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>A.4.10</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Deselect the first selected checkbox under 'Price Zone Type'</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".pointer.custom-checkbox-checked").first.click()`</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>A.4.11</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Re-select the first checkbox under 'Price Zone'</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").first.click()`</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>A.4.12</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Revisit the 'Price Zone' option</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Price Zone", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>A.4.13</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Select an additional checkbox under 'Price Zone'</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".filter-values.d-flex.align-items-center.p-l-32.p-r-24 &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>A.4.14</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Apply Filters' button</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>--- REFINE PRODUCT SELECTION USING HIERARCHY AND STYLE FILTERS ---</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>A.5</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Refine Product Selection Using Hierarchy and Style Filters</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>A.5.1</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Tiers' section</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(8) &gt; .zeb-tiers").click()`</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>A.5.2</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Open the 'Hierarchy' filter dropdown</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("#SideFilterproducthierarchyId").get_by_text("Hierarchy").click()`</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>A.5.3</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'Style Color' option</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Style Color").click()`</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>A.5.4</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Select a specific filter option</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; .filter-values.d-flex.align-items-center.p-l-32.p-r-12 &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>A.5.5</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Select another filter option</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(7) &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>A.5.6</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Apply the selected filters</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>--- SELECT OPTIMIZATION OBJECTIVE FOR THE PROMOTION ---</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr"/>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>A.6</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Select Optimization Objective for the Promotion</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>A.6.1</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Open the dropdown for selecting the optimization objective</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("#optimizationObjective &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>A.6.2</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Choose 'Optimize Sales Revenue'</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Optimize Sales Revenue$")).nth(1).click()`</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>--- ADD PRODUCTS TO THE PROMOTION FROM THE AVAILABLE PRODUCTS SECTION ---</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>A.7</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Add Products to the Promotion</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>A.7.1</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Navigate to the 'Available Products' section</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Available Products").click()`</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>A.7.2</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Open the first dropdown in the 'Available Products' section</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".dropdown-caret").first.click()`</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>A.7.3</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Select the first product option</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".d-flex.dropdown-option.align-items-center.p-v-5.p-l-32 &gt; .d-flex").first.click()`</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>A.7.4</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Open another dropdown for additional product selection</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(2) &gt; div &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>A.7.5</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Select the first option from the dropdown</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".d-flex.dropdown-option").first.click()`</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>A.7.6</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Click on a specific product from the list</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".overflow-auto &gt; div:nth-child(2)").click()`</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>A.7.7</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Open the third dropdown for further product selection</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div:nth-child(3) &gt; div &gt; esp-multiselect-dropdown &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>A.7.8</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Select the first option from the dropdown</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center").first.click()`</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>A.7.9</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Select the product '203_Logo Knits'</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("203_Logo Knits").click()`</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>A.7.10</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Apply the complex filter settings</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("complex-filter-apply").click()`</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>--- PERFORM ACTIONS ON PROMOTIONS (ADD, REOPTIMIZE, CONFIRM ACTIONS) ---</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr"/>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>A.8</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Perform Actions on Promotions</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>A.8.1</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Select the first promotion row</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".ag-row-odd &gt; .ag-cell &gt; .ag-cell-wrapper").first.click()`</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>A.8.2</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Actions' button</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("promotions-action-button").click()`</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>A.8.3</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'Add' option</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Add").click()`</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>A.8.4</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the addition of the new promotion</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>A.8.5</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Click the 'Reoptimize' button</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="Reoptimize").click()`</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>A.8.6</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the reoptimization action</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>--- CONFIGURE DISCOUNT ADJUSTMENTS (PERCENTAGE, PRICE ZONE ADJUSTMENTS, ROUNDING RULES) ---</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr"/>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>A.9</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Configure Discount Adjustments</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>A.9.1</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Off' input field</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("#off").click()`</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>A.9.2</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Set the discount percentage to '30'</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("#off").fill("30")`</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>A.9.3</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'Price Zone Adjustment' option</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Price Zone Adjustment").click()`</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>A.9.4</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Open the dropdown menu for rounding rules</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("#rounding_rules_id &gt; .multiselect-dropdown &gt; div &gt; .w-100 &gt; .d-flex.align-items-center &gt; .dropdown-caret").click()`</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>A.9.5</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Select the rounding rule '.99 RN'</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^\.99 RN$")).nth(1).click()`</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>A.9.6</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Attribute Value' input field</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("#attribute_value").click()`</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>A.9.7</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Set the attribute value to '35'</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator("#attribute_value").fill("35")`</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>--- REPLICATE ADJUSTMENTS ACROSS PROMOTIONS ---</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr"/>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>A.10</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Replicate Adjustments Across Promotions</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr"/>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>A.10.1</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Open the dropdown menu to configure additional settings</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".dropdown-caret").first.click()`</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>A.10.2</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Reopen the dropdown menu to finalize the configuration</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>`page.locator(".dropdown-caret").first.click()`</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>A.10.3</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Click the 'Apply' button to replicate adjustments</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("replicate-apply").click()`</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>--- NAVIGATE TO PRODUCT-LEVEL DETAILS PAGE FOR FURTHER ANALYSIS ---</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr"/>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>A.11</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Navigate to Product-Level Details Page</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr"/>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>A.11.1</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Navigate to the 'Product-Level Details' page</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>`page.goto("https://stage.mkr.esp.antuit.ai/nglcp/product-level-details/product-details")`</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>

--- a/UAT_Excel_Reports/Promo Discount_UAT.xlsx
+++ b/UAT_Excel_Reports/Promo Discount_UAT.xlsx
@@ -496,44 +496,18 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>--- NAVIGATE TO PROMOTIONS LANDING PAGE AND ACCESS PROMOTIONS MANAGEMENT SECTION ---</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -604,20 +578,11 @@
       <c r="F7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>--- CREATE A NEW PROMOTION AND ENTER BASIC PROMOTION DETAILS (NAME, DESCRIPTION, DATES) ---</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -856,20 +821,11 @@
       <c r="F18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>--- CONFIGURE PRICING OPTIONS (ASAP PRICING, REGULAR PRICING) ---</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -940,20 +896,11 @@
       <c r="F22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>--- APPLY HIERARCHY FILTERS (REGION, PRICE ZONE TYPE, PRICE ZONE) ---</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1312,20 +1259,11 @@
       <c r="F38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>--- REFINE PRODUCT SELECTION USING HIERARCHY AND STYLE FILTERS ---</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1492,20 +1430,11 @@
       <c r="F46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>--- SELECT OPTIMIZATION OBJECTIVE FOR THE PROMOTION ---</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr"/>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1576,20 +1505,11 @@
       <c r="F50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>--- ADD PRODUCTS TO THE PROMOTION FROM THE AVAILABLE PRODUCTS SECTION ---</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr"/>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1852,20 +1772,11 @@
       <c r="F62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>--- PERFORM ACTIONS ON PROMOTIONS (ADD, REOPTIMIZE, CONFIRM ACTIONS) ---</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr"/>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -2032,20 +1943,11 @@
       <c r="F70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>--- CONFIGURE DISCOUNT ADJUSTMENTS (PERCENTAGE, PRICE ZONE ADJUSTMENTS, ROUNDING RULES) ---</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr"/>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2236,20 +2138,11 @@
       <c r="F79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>--- REPLICATE ADJUSTMENTS ACROSS PROMOTIONS ---</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr"/>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2344,20 +2237,11 @@
       <c r="F84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>--- NAVIGATE TO PRODUCT-LEVEL DETAILS PAGE FOR FURTHER ANALYSIS ---</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr"/>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr"/>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -2404,8 +2288,20 @@
       <c r="F87" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="13">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
